--- a/output/pdf_financials_xlsx/RMI.xlsx
+++ b/output/pdf_financials_xlsx/RMI.xlsx
@@ -4478,13 +4478,13 @@
         <v>0.003482</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.022995</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>0.008983</v>
       </c>
       <c r="K103" s="1" t="inlineStr">
         <is>
@@ -4595,13 +4595,13 @@
         <v>0.115939</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.12271</v>
+        <v>-0.099715</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.019538</v>
+        <v>-0.002462</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.012051</v>
+        <v>0.021034</v>
       </c>
       <c r="K106" s="1" t="inlineStr">
         <is>
@@ -5924,7 +5924,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -7324,7 +7328,11 @@
           <t>Prepaids and deposits (Note 3)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.001688</v>
       </c>
@@ -7838,7 +7846,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RMI.xlsx
+++ b/output/pdf_financials_xlsx/RMI.xlsx
@@ -757,31 +757,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.269222</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.454075</v>
+        <v>2.318658</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.332679</v>
+        <v>1.217116</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.707257</v>
+        <v>1.818068</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.075365</v>
+        <v>1.745943</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.153103</v>
+        <v>0.517188</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.154429</v>
+        <v>0.381659</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.15</v>
+        <v>0.257204</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.15</v>
+        <v>0.287292</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.269222</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-2.318658</v>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.006822</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>-0.269222</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.311836</v>
+        <v>-2.318658</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.232786</v>
@@ -1537,7 +1537,7 @@
         <v>-0.269222</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.311836</v>
+        <v>-2.318658</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.232786</v>
@@ -1733,31 +1733,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.316051</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.084788</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.05753</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.046046</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.361852</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.18958</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.320354</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.114468</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.032294</v>
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
@@ -1811,31 +1811,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.316051</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.084788</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.05753</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.046046</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.361852</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.18958</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.320354</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.114468</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.032294</v>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
@@ -2279,31 +2279,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.318966</v>
+        <v>0.002915</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.220124</v>
+        <v>0.135336</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.107823</v>
+        <v>0.050293</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.105733</v>
+        <v>0.059687</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.442894</v>
+        <v>0.081042</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.225161</v>
+        <v>0.035581</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.330751</v>
+        <v>0.010397</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.14521</v>
+        <v>0.030742</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.055711</v>
+        <v>0.023417</v>
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">

--- a/output/pdf_financials_xlsx/RMI.xlsx
+++ b/output/pdf_financials_xlsx/RMI.xlsx
@@ -2921,31 +2921,31 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.016086</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.028865</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.037183</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.128345</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.093496</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.085136</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.047739</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.062789</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.076875</v>
       </c>
       <c r="K64" s="1" t="inlineStr">
         <is>
@@ -3041,28 +3041,28 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.009650000000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.061466</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.295724</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0664</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.195029</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.13896</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.143448</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.141413</v>
       </c>
       <c r="K67" s="1" t="inlineStr">
         <is>
@@ -8944,7 +8944,11 @@
           <t>Loan repayment through private placement</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
